--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487045_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487045_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7864</v>
+        <v>8.735200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8557</v>
+        <v>7.4566</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9306</v>
+        <v>1.2786</v>
       </c>
       <c r="G2" t="n">
         <v>4.9268</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.045</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6993</v>
+        <v>-0.0985</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3457</v>
+        <v>0.0023</v>
       </c>
       <c r="V2" t="n">
         <v>4.8696</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6662</v>
+        <v>5.8978</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4484</v>
+        <v>2.9477</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2178</v>
+        <v>2.9501</v>
       </c>
       <c r="G3" t="n">
         <v>3.2993</v>
@@ -688,13 +688,13 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7529</v>
+        <v>0.9845</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7549</v>
+        <v>0.2542</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9981</v>
+        <v>0.7304</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4047</v>
+        <v>4.3244</v>
       </c>
       <c r="E4" t="n">
         <v>5.0714</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6667</v>
+        <v>-0.747</v>
       </c>
       <c r="G4" t="n">
         <v>5.3046</v>
@@ -766,13 +766,13 @@
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7648</v>
+        <v>-0.8451</v>
       </c>
       <c r="T4" t="n">
         <v>-0.5354</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2294</v>
+        <v>-0.3097</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3281</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5572</v>
+        <v>2.577</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5119</v>
+        <v>1.6121</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0453</v>
+        <v>0.9649</v>
       </c>
       <c r="G5" t="n">
         <v>1.5849</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5718</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7733</v>
+        <v>-0.6732</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2016</v>
+        <v>0.1213</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7319</v>
+        <v>-0.0339</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7153</v>
+        <v>-1.0647</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4472</v>
+        <v>1.0308</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3601</v>
+        <v>1.5766</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5297</v>
+        <v>2.0535</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8304</v>
+        <v>-0.477</v>
       </c>
       <c r="J6" t="n">
-        <v>1.425</v>
+        <v>1.8694</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3764</v>
+        <v>1.7801</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0486</v>
+        <v>0.0893</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9351</v>
+        <v>-0.2928</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1533</v>
+        <v>0.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7818000000000001</v>
+        <v>-0.5662</v>
       </c>
       <c r="P6" t="n">
         <v>-1.5441</v>
@@ -922,28 +922,28 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4297</v>
+        <v>-0.0664</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7549</v>
+        <v>-0.039</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6748</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8222</v>
+        <v>-0.1773</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6655</v>
+        <v>-1.1159</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8434</v>
+        <v>0.9386</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5766</v>
+        <v>2.3601</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0535</v>
+        <v>1.5297</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.477</v>
+        <v>0.8304</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8694</v>
+        <v>1.425</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7801</v>
+        <v>1.3764</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0893</v>
+        <v>0.0486</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2928</v>
+        <v>0.9351</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2734</v>
+        <v>0.1533</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5662</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>-1.5441</v>
@@ -1000,22 +1000,22 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8547</v>
+        <v>0.5205</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6398</v>
+        <v>0.3543</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2148</v>
+        <v>0.1662</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2508</v>
+        <v>-1.1705</v>
       </c>
       <c r="E8" t="n">
         <v>-1.8735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6227</v>
+        <v>0.703</v>
       </c>
       <c r="G8" t="n">
         <v>0.3283</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.035</v>
+        <v>0.0453</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1434</v>
+        <v>0.2237</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALDA IRAOLA</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9347</v>
+        <v>-2.1109</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9946</v>
+        <v>-1.5268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0599</v>
+        <v>-0.5841</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1694</v>
+        <v>-2.2952</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.22</v>
+        <v>-2.8328</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0507</v>
+        <v>0.5376</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0282</v>
+        <v>-1.1208</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2317</v>
+        <v>-1.2836</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2035</v>
+        <v>0.1628</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1411</v>
+        <v>-1.1744</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9883</v>
+        <v>-1.5493</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1528</v>
+        <v>0.3748</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>1.158</v>
+        <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2346</v>
+        <v>-0.8157</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1917</v>
+        <v>-0.4759</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0429</v>
+        <v>-0.3398</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>A. ALDA IRAOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4321</v>
+        <v>-2.362</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5268</v>
+        <v>-2.3951</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9053</v>
+        <v>0.0331</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.2952</v>
+        <v>-2.1694</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8328</v>
+        <v>-2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5376</v>
+        <v>0.0507</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1208</v>
+        <v>-1.0282</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2836</v>
+        <v>-1.2317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1628</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1744</v>
+        <v>-1.1411</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5493</v>
+        <v>-0.9883</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3748</v>
+        <v>-0.1528</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1369</v>
+        <v>-0.1927</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4759</v>
+        <v>-0.2089</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.661</v>
+        <v>0.0162</v>
       </c>
       <c r="V10" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9305</v>
+        <v>-2.9037</v>
       </c>
       <c r="E11" t="n">
         <v>-5.0568</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1263</v>
+        <v>2.1531</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1644</v>
@@ -1312,13 +1312,13 @@
         <v>1.158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6273</v>
+        <v>0.654</v>
       </c>
       <c r="T11" t="n">
         <v>0.0278</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5995</v>
+        <v>0.6263</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6562</v>
@@ -1348,10 +1348,10 @@
         <v>12.7761</v>
       </c>
       <c r="E12" t="n">
-        <v>4.054900000000001</v>
+        <v>4.054999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>8.7212</v>
+        <v>8.7211</v>
       </c>
       <c r="G12" t="n">
         <v>13.7516</v>
@@ -1366,10 +1366,10 @@
         <v>14.8809</v>
       </c>
       <c r="K12" t="n">
-        <v>5.944700000000001</v>
+        <v>5.944699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>8.936100000000001</v>
+        <v>8.9361</v>
       </c>
       <c r="M12" t="n">
         <v>-1.1292</v>
@@ -1390,10 +1390,10 @@
         <v>13.5107</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3637000000000001</v>
+        <v>-0.3636999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5729</v>
+        <v>-1.5731</v>
       </c>
       <c r="U12" t="n">
         <v>1.2094</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7092</v>
+        <v>4.1071</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2261</v>
+        <v>2.0258</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4831</v>
+        <v>2.0813</v>
       </c>
       <c r="G13" t="n">
         <v>3.2969</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3074</v>
+        <v>0.7053</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2803</v>
+        <v>0.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0271</v>
+        <v>0.6253</v>
       </c>
       <c r="V13" t="n">
         <v>1.842</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8381</v>
+        <v>2.3863</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0268</v>
+        <v>0.6047</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1886</v>
+        <v>1.7816</v>
       </c>
       <c r="G14" t="n">
-        <v>0.451</v>
+        <v>0.8762</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2636</v>
+        <v>1.5017</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8125</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8073</v>
+        <v>1.8437</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7994</v>
+        <v>1.9093</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3562</v>
+        <v>-0.9674</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5358</v>
+        <v>-0.4076</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8204</v>
+        <v>-0.5598</v>
       </c>
       <c r="P14" t="n">
-        <v>0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.965</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>2.252</v>
+        <v>-0.034</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9566</v>
+        <v>-0.2739</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2954</v>
+        <v>0.2399</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4203</v>
+        <v>2.1417</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5044999999999999</v>
+        <v>3.6248</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9158</v>
+        <v>-1.4831</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8762</v>
+        <v>0.451</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5017</v>
+        <v>1.2636</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.8125</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8437</v>
+        <v>2.8073</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9093</v>
+        <v>2.7994</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9674</v>
+        <v>-2.3562</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4076</v>
+        <v>-1.5358</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5598</v>
+        <v>-0.8204</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5441</v>
+        <v>0.193</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0.5556</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3741</v>
+        <v>0.5546</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3741</v>
+        <v>0.001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2317</v>
+        <v>0.4925</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4345</v>
+        <v>-0.3344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6663</v>
+        <v>0.8269</v>
       </c>
       <c r="G16" t="n">
         <v>0.0215</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3688</v>
+        <v>-0.1081</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1071</v>
+        <v>0.2677</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0997</v>
+        <v>-0.2398</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0566</v>
+        <v>-0.2439</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1563</v>
+        <v>0.004</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0361</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2796</v>
+        <v>-0.4197</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2551</v>
+        <v>-0.5555</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0245</v>
+        <v>0.1358</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5036</v>
+        <v>-0.577</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0318</v>
+        <v>-0.0684</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5354</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1791</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4475</v>
+        <v>0.3741</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3153</v>
+        <v>0.3421</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0024</v>
+        <v>-2.7197</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3583</v>
+        <v>-1.5027</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.644</v>
+        <v>-1.2171</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1208</v>
+        <v>-3.7917</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0402</v>
+        <v>-2.0431</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0807</v>
+        <v>-1.7486</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1336</v>
+        <v>-1.6494</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8798</v>
+        <v>-1.1282</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2538</v>
+        <v>-0.5212</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9872</v>
+        <v>-2.1423</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1604</v>
+        <v>-0.9149</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8268</v>
+        <v>-1.2274</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7674</v>
+        <v>0.3698</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7403</v>
+        <v>0.1468</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0271</v>
+        <v>0.2231</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6547</v>
+        <v>-2.9617</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3038</v>
+        <v>-2.5586</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3509</v>
+        <v>-0.4031</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7917</v>
+        <v>-3.1208</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0431</v>
+        <v>-1.0402</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7486</v>
+        <v>-2.0807</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6494</v>
+        <v>-2.1336</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1282</v>
+        <v>-0.8798</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5212</v>
+        <v>-1.2538</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1423</v>
+        <v>-0.9872</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9149</v>
+        <v>-0.1604</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2274</v>
+        <v>-0.8268</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5651</v>
+        <v>0.8081</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6544</v>
+        <v>0.54</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0892</v>
+        <v>0.268</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2716</v>
+        <v>-3.3564</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2254</v>
+        <v>-1.5244</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0462</v>
+        <v>-1.832</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3651</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1647</v>
+        <v>-0.2495</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0708</v>
+        <v>-0.3698</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0939</v>
+        <v>0.1203</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6044</v>
+        <v>-5.0901</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2126</v>
+        <v>-4.9122</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3917</v>
+        <v>-0.1779</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5769</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.0416</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5063</v>
+        <v>-0.2059</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0496</v>
+        <v>0.1642</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4716</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8392</v>
+        <v>-6.2912</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0321</v>
+        <v>-3.8318</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8071</v>
+        <v>-2.4594</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3276</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4766</v>
+        <v>-0.9287</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9822</v>
+        <v>-0.7819</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4944</v>
+        <v>-0.1468</v>
       </c>
       <c r="V23" t="n">
         <v>-1.842</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.7763</v>
+        <v>-12.1083</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.720899999999999</v>
+        <v>-8.7211</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.055</v>
+        <v>-3.3874</v>
       </c>
       <c r="G24" t="n">
         <v>-13.7517</v>
@@ -2326,13 +2326,13 @@
         <v>18.3358</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3635999999999999</v>
+        <v>1.0313</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2094</v>
+        <v>-1.2093</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5729</v>
+        <v>2.2406</v>
       </c>
       <c r="V24" t="n">
         <v>-4.2134</v>
